--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008426604091929184</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31855649</v>
+        <v>4185503</v>
       </c>
       <c r="L2" t="n">
-        <v>18103964</v>
+        <v>2067254</v>
       </c>
       <c r="M2" t="n">
-        <v>4454266</v>
+        <v>438092</v>
       </c>
       <c r="N2" t="n">
-        <v>232139</v>
+        <v>14542</v>
       </c>
       <c r="O2" t="n">
-        <v>2653860</v>
+        <v>257528</v>
       </c>
       <c r="P2" t="n">
-        <v>1046471</v>
+        <v>102532</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999873042106628</v>
+        <v>0.9999875426292419</v>
       </c>
       <c r="R2" t="n">
-        <v>0.887506902217865</v>
+        <v>0.7997147440910339</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7806234359741211</v>
+        <v>0.6286792755126953</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7277913689613342</v>
+        <v>0.5330215096473694</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3709493577480316</v>
+        <v>0.1007726714015007</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7749770283699036</v>
+        <v>0.5875047445297241</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8499546647071838</v>
+        <v>0.7170220613479614</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201955565764127</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>31855649</v>
+        <v>4185503</v>
       </c>
       <c r="E3" t="n">
-        <v>3458372</v>
+        <v>822928</v>
       </c>
       <c r="F3" t="n">
-        <v>74354</v>
+        <v>24465</v>
       </c>
       <c r="G3" t="n">
-        <v>7887</v>
+        <v>2587</v>
       </c>
       <c r="H3" t="n">
-        <v>4107</v>
+        <v>1476</v>
       </c>
       <c r="I3" t="n">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="J3" t="n">
-        <v>70486777</v>
+        <v>10069541</v>
       </c>
       <c r="K3" t="n">
-        <v>75473631</v>
+        <v>10330700</v>
       </c>
       <c r="L3" t="n">
-        <v>86827656</v>
+        <v>11893126</v>
       </c>
       <c r="M3" t="n">
-        <v>106702477</v>
+        <v>15095110</v>
       </c>
       <c r="N3" t="n">
-        <v>113892623</v>
+        <v>16196602</v>
       </c>
       <c r="O3" t="n">
-        <v>110574114</v>
+        <v>15724724</v>
       </c>
       <c r="P3" t="n">
-        <v>113373731</v>
+        <v>16182028</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8998616337776184</v>
+        <v>0.8309419751167297</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7872440814971924</v>
+        <v>0.6260840892791748</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6807121634483337</v>
+        <v>0.46750807762146</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3709956109523773</v>
+        <v>0.1622357368469238</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7439389228820801</v>
+        <v>0.5044998526573181</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7731409668922424</v>
+        <v>0.5298619866371155</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0318933357951476</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3804943</v>
+        <v>979144</v>
       </c>
       <c r="E4" t="n">
-        <v>18103964</v>
+        <v>2067254</v>
       </c>
       <c r="F4" t="n">
-        <v>953817</v>
+        <v>212109</v>
       </c>
       <c r="G4" t="n">
-        <v>48636</v>
+        <v>17874</v>
       </c>
       <c r="H4" t="n">
-        <v>78368</v>
+        <v>23156</v>
       </c>
       <c r="I4" t="n">
-        <v>6895</v>
+        <v>2338</v>
       </c>
       <c r="J4" t="n">
-        <v>563</v>
+        <v>79</v>
       </c>
       <c r="K4" t="n">
-        <v>4037761</v>
+        <v>1048242</v>
       </c>
       <c r="L4" t="n">
-        <v>5087710</v>
+        <v>1220995</v>
       </c>
       <c r="M4" t="n">
-        <v>1665985</v>
+        <v>383811</v>
       </c>
       <c r="N4" t="n">
-        <v>393658</v>
+        <v>129763</v>
       </c>
       <c r="O4" t="n">
-        <v>770577</v>
+        <v>180814</v>
       </c>
       <c r="P4" t="n">
-        <v>184737</v>
+        <v>40465</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999993622303009</v>
+        <v>0.9999937415122986</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8936415314674377</v>
+        <v>0.8150293827056885</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7839197516441345</v>
+        <v>0.6273790001869202</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7034649252891541</v>
+        <v>0.4981199502944946</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3709724843502045</v>
+        <v>0.1243224740028381</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7591409087181091</v>
+        <v>0.5428476333618164</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8097301721572876</v>
+        <v>0.609395444393158</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>155487</v>
+        <v>49692</v>
       </c>
       <c r="E5" t="n">
-        <v>1395457</v>
+        <v>325866</v>
       </c>
       <c r="F5" t="n">
-        <v>4454266</v>
+        <v>438092</v>
       </c>
       <c r="G5" t="n">
-        <v>140343</v>
+        <v>40173</v>
       </c>
       <c r="H5" t="n">
-        <v>366432</v>
+        <v>73984</v>
       </c>
       <c r="I5" t="n">
-        <v>31526</v>
+        <v>9265</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3544959</v>
+        <v>851555</v>
       </c>
       <c r="L5" t="n">
-        <v>4892670</v>
+        <v>1234625</v>
       </c>
       <c r="M5" t="n">
-        <v>2089272</v>
+        <v>498987</v>
       </c>
       <c r="N5" t="n">
-        <v>393580</v>
+        <v>75093</v>
       </c>
       <c r="O5" t="n">
-        <v>913449</v>
+        <v>252934</v>
       </c>
       <c r="P5" t="n">
-        <v>307061</v>
+        <v>90975</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999951124191284</v>
+        <v>0.9999951720237732</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9340128302574158</v>
+        <v>0.8842716217041016</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9131476283073425</v>
+        <v>0.8504130244255066</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9673205614089966</v>
+        <v>0.9462233185768127</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9931492209434509</v>
+        <v>0.9875209331512451</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9853450655937195</v>
+        <v>0.9735777378082275</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9957202076911926</v>
+        <v>0.9919931888580322</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>72581</v>
+        <v>16411</v>
       </c>
       <c r="E6" t="n">
-        <v>104909</v>
+        <v>22261</v>
       </c>
       <c r="F6" t="n">
-        <v>151324</v>
+        <v>25843</v>
       </c>
       <c r="G6" t="n">
-        <v>232139</v>
+        <v>14542</v>
       </c>
       <c r="H6" t="n">
-        <v>58842</v>
+        <v>9336</v>
       </c>
       <c r="I6" t="n">
-        <v>5842</v>
+        <v>1224</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>4573</v>
+        <v>2945</v>
       </c>
       <c r="E7" t="n">
-        <v>120970</v>
+        <v>46153</v>
       </c>
       <c r="F7" t="n">
-        <v>463735</v>
+        <v>112961</v>
       </c>
       <c r="G7" t="n">
-        <v>183775</v>
+        <v>63316</v>
       </c>
       <c r="H7" t="n">
-        <v>2653860</v>
+        <v>257528</v>
       </c>
       <c r="I7" t="n">
-        <v>140254</v>
+        <v>27546</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>8002</v>
+        <v>3787</v>
       </c>
       <c r="F8" t="n">
-        <v>22755</v>
+        <v>8433</v>
       </c>
       <c r="G8" t="n">
-        <v>13017</v>
+        <v>5813</v>
       </c>
       <c r="H8" t="n">
-        <v>262828</v>
+        <v>72862</v>
       </c>
       <c r="I8" t="n">
-        <v>1046471</v>
+        <v>102532</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
